--- a/Holdings14feb2026.xlsx
+++ b/Holdings14feb2026.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Investment\Inv_code_proj\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Investment\pms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CDAD64-BC6C-4839-8ECB-F1AD69B02014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE73C0E1-49C5-4671-BB8B-54EE7B20F198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase Date Wise" sheetId="6" r:id="rId1"/>
-    <sheet name="Company Wise Aggregated Data" sheetId="4" r:id="rId2"/>
-    <sheet name="GOLD&amp;SILVER" sheetId="10" r:id="rId3"/>
-    <sheet name="MMYY" sheetId="7" r:id="rId4"/>
-    <sheet name="YYYY" sheetId="8" r:id="rId5"/>
-    <sheet name="Large-Small-ETF" sheetId="15" r:id="rId6"/>
+    <sheet name="Dividend" sheetId="16" r:id="rId2"/>
+    <sheet name="RealizedP&amp;L" sheetId="17" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="216">
   <si>
     <t>ASIANPAINT</t>
   </si>
@@ -92,9 +89,6 @@
     <t>NMDC</t>
   </si>
   <si>
-    <t>OLAELEC-BE</t>
-  </si>
-  <si>
     <t>PNB</t>
   </si>
   <si>
@@ -167,9 +161,6 @@
     <t>KEC</t>
   </si>
   <si>
-    <t>SBISILVER</t>
-  </si>
-  <si>
     <t>GOLDIETF</t>
   </si>
   <si>
@@ -179,405 +170,524 @@
     <t>CONSUMBEES</t>
   </si>
   <si>
-    <t>PIRAMALFIN-BE</t>
-  </si>
-  <si>
     <t>PPLPHARMA</t>
   </si>
   <si>
-    <t>MMYY</t>
-  </si>
-  <si>
-    <t>Purchase Companies</t>
-  </si>
-  <si>
-    <t>inv_amount</t>
-  </si>
-  <si>
-    <t>AUG2022</t>
-  </si>
-  <si>
-    <t>GLAND
-PIRAMALFIN-BE
-PPLPHARMA</t>
-  </si>
-  <si>
-    <t>SEP2023</t>
-  </si>
-  <si>
-    <t>OCT2023</t>
-  </si>
-  <si>
-    <t>ITC
-ITCHOTELS
-SETFNN50</t>
-  </si>
-  <si>
-    <t>DEC2023</t>
-  </si>
-  <si>
-    <t>ITC
-ITCHOTELS
-KOTAKBANK</t>
-  </si>
-  <si>
-    <t>JAN2024</t>
-  </si>
-  <si>
-    <t>ITC
-ITCHOTELS</t>
-  </si>
-  <si>
-    <t>FEB2024</t>
-  </si>
-  <si>
-    <t>ITC
-ITCHOTELS
-SGBFEB32IV-GB</t>
-  </si>
-  <si>
-    <t>APR2024</t>
-  </si>
-  <si>
-    <t>HINDUNILVR
-IDFCFIRSTB
-PVRINOX
-SETFGOLD</t>
-  </si>
-  <si>
-    <t>MAY2024</t>
-  </si>
-  <si>
-    <t>JUN2024</t>
-  </si>
-  <si>
-    <t>SBIN
-SETFGOLD
-UJJIVANSFB</t>
-  </si>
-  <si>
-    <t>JUL2024</t>
-  </si>
-  <si>
-    <t>BANDHANBNK
-HDFCLIFE
-HINDUNILVR
-SBICARD
-SONATSOFTW</t>
-  </si>
-  <si>
-    <t>AUG2024</t>
-  </si>
-  <si>
-    <t>ASIANPAINT
-SBIN
-SETFGOLD</t>
-  </si>
-  <si>
-    <t>SEP2024</t>
-  </si>
-  <si>
-    <t>BANDHANBNK
-EQUITASBNK
-IDFCFIRSTB
-SBIN
-TATASTEEL</t>
-  </si>
-  <si>
-    <t>OCT2024</t>
-  </si>
-  <si>
-    <t>BIOCON
-HINDUNILVR
-PNB
-SBICARD
-SBIN</t>
-  </si>
-  <si>
-    <t>NOV2024</t>
-  </si>
-  <si>
-    <t>SETFGOLD
-SETFNIF50</t>
-  </si>
-  <si>
-    <t>DEC2024</t>
-  </si>
-  <si>
-    <t>PNBHOUSING
-SETFNN50</t>
-  </si>
-  <si>
-    <t>JAN2025</t>
-  </si>
-  <si>
-    <t>CDSL
-HDFCLIFE
-HINDUNILVR
-PNB
-PNBHOUSING
-SETFNN50
-TATASTEEL
-UJJIVANSFB
-VOLTAS</t>
-  </si>
-  <si>
-    <t>FEB2025</t>
-  </si>
-  <si>
-    <t>ASIANPAINT
-BIOCON
-VOLTAS</t>
-  </si>
-  <si>
-    <t>MAR2025</t>
-  </si>
-  <si>
-    <t>SETFNIF50
-SETFNN50
-SONATSOFTW
-TATAPOWER</t>
-  </si>
-  <si>
-    <t>APR2025</t>
-  </si>
-  <si>
-    <t>MAY2025</t>
-  </si>
-  <si>
-    <t>SETFGOLD
-VOLTAS</t>
-  </si>
-  <si>
-    <t>JUN2025</t>
-  </si>
-  <si>
-    <t>HAVELLS
-HINDUNILVR
-INFY
-ITC
-PNB
-SBIETFIT
-TCS</t>
-  </si>
-  <si>
-    <t>JUL2025</t>
-  </si>
-  <si>
-    <t>FMCGIETF
-ITC
-SBICARD</t>
-  </si>
-  <si>
-    <t>AUG2025</t>
-  </si>
-  <si>
-    <t>HDFCLIFE
-HDFCSILVER
-PNB
-PNBHOUSING</t>
-  </si>
-  <si>
-    <t>SEP2025</t>
-  </si>
-  <si>
-    <t>BANDHANBNK
-BIOCON
-CDSL
-FMCGIETF
-HDFCSILVER
-IDFCFIRSTB
-KEC
-MOTHERSON
-NMDC
-OLAELEC-BE
-PNBHOUSING
-SBICARD
-SETFGOLD
-SETFNN50
-UJJIVANSFB
-UNITDSPR
-VBL</t>
-  </si>
-  <si>
-    <t>OCT2025</t>
-  </si>
-  <si>
-    <t>CONSUMBEES
-FMCGIETF
-GOLDBEES
-GOLDIETF
-HDFCLIFE
-HDFCSILVER
-KOTAKBANK
-SBISILVER
-SETFGOLD
-VBL</t>
-  </si>
-  <si>
-    <t>NOV2025</t>
-  </si>
-  <si>
-    <t>YYYY</t>
-  </si>
-  <si>
-    <t>HINDUNILVR
-ITCHOTELS
-SETFNN50
-ITC
-ITCHOTELS
-KOTAKBANK</t>
-  </si>
-  <si>
     <t xml:space="preserve">	ANANTRAJ</t>
   </si>
   <si>
-    <t>GOLDBEES
-HDFCSILVER
-KEC
-ANANTRAJ</t>
-  </si>
-  <si>
-    <t>ASIANPAINT
-BANDHANBNK
-BIOCON
-CDSL
-CONSUMBEES
-FMCGIETF
-GOLDBEES
-GOLDIETF
-HAVELLS
-HDFCLIFE
-HDFCSILVER
-HINDUNILVR
-IDFCFIRSTB
-INFY
-ITC
-KEC
-KOTAKBANK
-MOTHERSON
-NMDC
-OLAELEC-BE
-PNB
-PNBHOUSING
-SBICARD
-SBIETFIT
-SBISILVER
-SETFGOLD
-SETFNIF50
-SETFNN50
-SONATSOFTW
-TATAPOWER
-TATASTEEL
-TCS
-UJJIVANSFB
-UNITDSPR
-VBL
-VOLTAS
-ANANTRAJ</t>
-  </si>
-  <si>
-    <t>ASIANPAINT
-BANDHANBNK
-EQUITASBNK
-HDFCLIFE
-HINDUNILVR
-IDFCFIRSTB
-ITCHOTELS
-ITC
-KOTAKBANK
-PNB
-PNBHOUSING
-PVRINOX
-SBICARD
-SBIN
-SGBFEB32IV-GB
-SETFGOLD
-SETFNIF50
-SETFNN50
-SONATSOFTW
-TATASTEEL
-UJJIVANSFB
-BIOCON</t>
-  </si>
-  <si>
     <t xml:space="preserve">	CGPOWER</t>
   </si>
   <si>
-    <t>SGBFEB32IV</t>
-  </si>
-  <si>
-    <t>DEC2025</t>
-  </si>
-  <si>
-    <t>HDFCLIFE
-CGPOWER
-ANANTRAJ
-OLAELEC</t>
-  </si>
-  <si>
-    <t>Instrument</t>
-  </si>
-  <si>
-    <t>Qty.</t>
-  </si>
-  <si>
-    <t>Avg. cost</t>
-  </si>
-  <si>
-    <t>Invested</t>
+    <t>CGPOWER</t>
+  </si>
+  <si>
+    <t>NBCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	HYUNDAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	MAXHEALTH</t>
+  </si>
+  <si>
+    <t>TATSILV</t>
+  </si>
+  <si>
+    <t>CHEMICAL</t>
+  </si>
+  <si>
+    <t>29/02/2024</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
+    <t>Ex-Date</t>
+  </si>
+  <si>
+    <t>Dividend Per Share</t>
+  </si>
+  <si>
+    <t>Net Dividend Amount</t>
+  </si>
+  <si>
+    <t>FY</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
+  </si>
+  <si>
+    <t>2022-10-27</t>
+  </si>
+  <si>
+    <t>2022-2023</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>INE669C01036</t>
+  </si>
+  <si>
+    <t>2022-11-09</t>
+  </si>
+  <si>
+    <t>VEDL</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>2022-11-29</t>
+  </si>
+  <si>
+    <t>WIPRO</t>
+  </si>
+  <si>
+    <t>INE075A01022</t>
+  </si>
+  <si>
+    <t>2023-01-24</t>
+  </si>
+  <si>
+    <t>OFSS</t>
+  </si>
+  <si>
+    <t>INE881D01027</t>
+  </si>
+  <si>
+    <t>2023-05-09</t>
+  </si>
+  <si>
+    <t>2023-2024</t>
+  </si>
+  <si>
+    <t>2023-06-02</t>
+  </si>
+  <si>
+    <t>PEL</t>
+  </si>
+  <si>
+    <t>INE140A01024</t>
+  </si>
+  <si>
+    <t>2023-06-16</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>2023-06-22</t>
+  </si>
+  <si>
+    <t>2023-07-21</t>
+  </si>
+  <si>
+    <t>UPL</t>
+  </si>
+  <si>
+    <t>INE628A01036</t>
+  </si>
+  <si>
+    <t>2023-08-03</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>2023-08-14</t>
+  </si>
+  <si>
+    <t>2023-10-25</t>
+  </si>
+  <si>
+    <t>2023-11-02</t>
+  </si>
+  <si>
+    <t>INE030A01027</t>
+  </si>
+  <si>
+    <t>2024-01-24</t>
+  </si>
+  <si>
+    <t>INE154A01025</t>
+  </si>
+  <si>
+    <t>2024-02-08</t>
+  </si>
+  <si>
+    <t>INE018E01016</t>
+  </si>
+  <si>
+    <t>2024-03-28</t>
+  </si>
+  <si>
+    <t>HDFCBANK</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
+  </si>
+  <si>
+    <t>2024-05-10</t>
+  </si>
+  <si>
+    <t>2024-2025</t>
+  </si>
+  <si>
+    <t>2024-05-31</t>
+  </si>
+  <si>
+    <t>2024-06-04</t>
+  </si>
+  <si>
+    <t>2024-06-14</t>
+  </si>
+  <si>
+    <t>INE376G01013</t>
+  </si>
+  <si>
+    <t>2024-07-05</t>
+  </si>
+  <si>
+    <t>INE0DK501011</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>INE551W01018</t>
+  </si>
+  <si>
+    <t>INE237A01028</t>
+  </si>
+  <si>
+    <t>2024-07-19</t>
+  </si>
+  <si>
+    <t>INE269A01021</t>
+  </si>
+  <si>
+    <t>2024-07-26</t>
+  </si>
+  <si>
+    <t>CUB</t>
+  </si>
+  <si>
+    <t>INE491A01021</t>
+  </si>
+  <si>
+    <t>2024-08-09</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>BANDHANBNK6</t>
+  </si>
+  <si>
+    <t>INE545U01014</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>INE068V01023</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>2024-11-06</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2025-02-12</t>
+  </si>
+  <si>
+    <t>2025-02-25</t>
+  </si>
+  <si>
+    <t>SBIN#</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>2025-05-16</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>TATACONSUM</t>
+  </si>
+  <si>
+    <t>INE192A01025</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>2025-06-06</t>
+  </si>
+  <si>
+    <t>2025-06-10</t>
+  </si>
+  <si>
+    <t>2025-06-13</t>
+  </si>
+  <si>
+    <t>INE160A01022</t>
+  </si>
+  <si>
+    <t>2025-06-20</t>
+  </si>
+  <si>
+    <t>INE226A01021</t>
+  </si>
+  <si>
+    <t>INE245A01021</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>HINDUNILVR#</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>2025-07-04</t>
+  </si>
+  <si>
+    <t>INE092T01019</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>2025-07-18</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>PNBHOUSING#</t>
+  </si>
+  <si>
+    <t>INE572E01012</t>
+  </si>
+  <si>
+    <t>2025-08-01</t>
+  </si>
+  <si>
+    <t>INE736A01011</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>INFY#</t>
+  </si>
+  <si>
+    <t>2025-10-27</t>
+  </si>
+  <si>
+    <t>2025-11-07</t>
+  </si>
+  <si>
+    <t>2025-11-18</t>
+  </si>
+  <si>
+    <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>2026-01-16</t>
+  </si>
+  <si>
+    <t>HAVELLS#</t>
+  </si>
+  <si>
+    <t>INE176B01034</t>
+  </si>
+  <si>
+    <t>2026-01-23</t>
+  </si>
+  <si>
+    <t>INE854D01024</t>
+  </si>
+  <si>
+    <t>2026-01-27</t>
+  </si>
+  <si>
+    <t>INE067A01029</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>ITC#</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>Buy Value</t>
+  </si>
+  <si>
+    <t>Sell Value</t>
+  </si>
+  <si>
+    <t>Realized P&amp;L</t>
+  </si>
+  <si>
+    <t>AUTOIETF</t>
+  </si>
+  <si>
+    <t>INF109KC10V2</t>
+  </si>
+  <si>
+    <t>COMMOIETF</t>
+  </si>
+  <si>
+    <t>INF109KC19O8</t>
+  </si>
+  <si>
+    <t>HDFCSILVER-E</t>
+  </si>
+  <si>
+    <t>INF179KC1DI2</t>
+  </si>
+  <si>
+    <t>MARICO</t>
+  </si>
+  <si>
+    <t>INE196A01026</t>
+  </si>
+  <si>
+    <t>MON100-E</t>
+  </si>
+  <si>
+    <t>INF247L01AP3</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>SAIL</t>
+  </si>
+  <si>
+    <t>INE114A01011</t>
+  </si>
+  <si>
+    <t>INF200KA1S14</t>
+  </si>
+  <si>
+    <t>SBISENSEX</t>
+  </si>
+  <si>
+    <t>INF200K01VT2</t>
+  </si>
+  <si>
+    <t>SBISILVER-E</t>
+  </si>
+  <si>
+    <t>INF200KB1217</t>
+  </si>
+  <si>
+    <t>SETFBSE100</t>
+  </si>
+  <si>
+    <t>INF200KA1572</t>
+  </si>
+  <si>
+    <t>SETFGOLD-E</t>
+  </si>
+  <si>
+    <t>INF200KA16D8</t>
+  </si>
+  <si>
+    <t>INF200KA1FS1</t>
+  </si>
+  <si>
+    <t>SETFNIFBK</t>
+  </si>
+  <si>
+    <t>INF200KA1580</t>
+  </si>
+  <si>
+    <t>COHANCE</t>
+  </si>
+  <si>
+    <t>INE03QK01018</t>
+  </si>
+  <si>
+    <t>PIRAMALFIN</t>
   </si>
   <si>
     <t>OLAELEC</t>
   </si>
   <si>
-    <t>PIRAMALFIN</t>
-  </si>
-  <si>
-    <t>ANANTRAJ</t>
-  </si>
-  <si>
-    <t>CGPOWER</t>
-  </si>
-  <si>
-    <t>Group Wise Total</t>
-  </si>
-  <si>
-    <t>NBCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	HYUNDAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	MAXHEALTH</t>
-  </si>
-  <si>
-    <t>LTP</t>
-  </si>
-  <si>
-    <t>Cur. val</t>
-  </si>
-  <si>
-    <t>HYUNDAI</t>
-  </si>
-  <si>
-    <t>MAXHEALTH</t>
-  </si>
-  <si>
-    <t>TATSILV</t>
-  </si>
-  <si>
-    <t>CHEMICAL</t>
-  </si>
-  <si>
-    <t>29/02/2024</t>
+    <t>27/09/2023</t>
+  </si>
+  <si>
+    <t>KWIL</t>
+  </si>
+  <si>
+    <t>23/10/2024</t>
+  </si>
+  <si>
+    <t>25/10/2024</t>
+  </si>
+  <si>
+    <t>26/06/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -734,17 +844,60 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -924,8 +1077,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1040,21 +1199,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1099,9 +1243,9 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1128,20 +1272,44 @@
     <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="17" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="19" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="42" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="42" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1498,7 +1666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A34EE69-FFA9-4CB2-92C6-25BBB6E0EE9A}">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E156"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1506,24 +1674,26 @@
     <col min="3" max="3" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="8" max="8" width="23.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2683,7 +2853,7 @@
         <v>45908</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="C66" s="10">
         <v>200</v>
@@ -2701,7 +2871,7 @@
         <v>46011</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="C67" s="2">
         <v>300</v>
@@ -2719,7 +2889,7 @@
         <v>46050</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="C68" s="2">
         <v>100</v>
@@ -2737,7 +2907,7 @@
         <v>45596</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C69" s="10">
         <v>150</v>
@@ -2755,7 +2925,7 @@
         <v>45671</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C70" s="10">
         <v>130</v>
@@ -2773,7 +2943,7 @@
         <v>45828</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C71" s="10">
         <v>120</v>
@@ -2791,7 +2961,7 @@
         <v>45873</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C72" s="10">
         <v>100</v>
@@ -2809,7 +2979,7 @@
         <v>45631</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C73" s="10">
         <v>30</v>
@@ -2827,7 +2997,7 @@
         <v>45672</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C74" s="10">
         <v>20</v>
@@ -2845,7 +3015,7 @@
         <v>45870</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C75" s="10">
         <v>10</v>
@@ -2863,7 +3033,7 @@
         <v>45915</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C76" s="10">
         <v>10</v>
@@ -2881,7 +3051,7 @@
         <v>45384</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C77" s="10">
         <v>10</v>
@@ -2899,7 +3069,7 @@
         <v>45474</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C78" s="10">
         <v>20</v>
@@ -2917,7 +3087,7 @@
         <v>45595</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C79" s="10">
         <v>20</v>
@@ -2935,7 +3105,7 @@
         <v>45846</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C80" s="10">
         <v>60</v>
@@ -2953,7 +3123,7 @@
         <v>45901</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C81" s="10">
         <v>20</v>
@@ -2971,7 +3141,7 @@
         <v>45811</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C82" s="10">
         <v>100</v>
@@ -2989,7 +3159,7 @@
         <v>45812</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C83" s="10">
         <v>100</v>
@@ -3007,7 +3177,7 @@
         <v>45448</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C84" s="10">
         <v>25</v>
@@ -3025,7 +3195,7 @@
         <v>45520</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C85" s="10">
         <v>30</v>
@@ -3043,7 +3213,7 @@
         <v>45554</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C86" s="10">
         <v>30</v>
@@ -3061,7 +3231,7 @@
         <v>45595</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C87" s="10">
         <v>15</v>
@@ -3079,7 +3249,7 @@
         <v>45398</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C88" s="10">
         <v>777</v>
@@ -3097,7 +3267,7 @@
         <v>45454</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C89" s="10">
         <v>841</v>
@@ -3115,7 +3285,7 @@
         <v>45511</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C90" s="10">
         <v>1671</v>
@@ -3133,7 +3303,7 @@
         <v>45607</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C91" s="10">
         <v>1500</v>
@@ -3151,7 +3321,7 @@
         <v>45771</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C92" s="10">
         <v>711</v>
@@ -3169,7 +3339,7 @@
         <v>45779</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C93" s="10">
         <v>400</v>
@@ -3187,7 +3357,7 @@
         <v>45791</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C94" s="10">
         <v>500</v>
@@ -3205,7 +3375,7 @@
         <v>45908</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C95" s="10">
         <v>100</v>
@@ -3223,7 +3393,7 @@
         <v>45930</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C96" s="10">
         <v>100</v>
@@ -3241,7 +3411,7 @@
         <v>45940</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C97" s="10">
         <v>100</v>
@@ -3259,7 +3429,7 @@
         <v>45961</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C98" s="10">
         <v>100</v>
@@ -3277,7 +3447,7 @@
         <v>46044</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C99" s="2">
         <v>700</v>
@@ -3295,7 +3465,7 @@
         <v>45615</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C100" s="10">
         <v>50</v>
@@ -3313,7 +3483,7 @@
         <v>45721</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C101" s="10">
         <v>100</v>
@@ -3331,7 +3501,7 @@
         <v>45222</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C102" s="10">
         <v>1</v>
@@ -3349,7 +3519,7 @@
         <v>45645</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C103" s="10">
         <v>11</v>
@@ -3367,7 +3537,7 @@
         <v>45663</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C104" s="10">
         <v>13</v>
@@ -3385,7 +3555,7 @@
         <v>45721</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C105" s="10">
         <v>45</v>
@@ -3403,7 +3573,7 @@
         <v>45930</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C106" s="10">
         <v>30</v>
@@ -3418,10 +3588,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C107" s="10">
         <v>16</v>
@@ -3439,7 +3609,7 @@
         <v>45484</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C108" s="10">
         <v>20</v>
@@ -3457,7 +3627,7 @@
         <v>45734</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C109" s="10">
         <v>30</v>
@@ -3475,7 +3645,7 @@
         <v>45723</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C110" s="10">
         <v>100</v>
@@ -3493,7 +3663,7 @@
         <v>46036</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C111" s="10">
         <v>20</v>
@@ -3511,7 +3681,7 @@
         <v>46038</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C112" s="10">
         <v>5</v>
@@ -3529,7 +3699,7 @@
         <v>45818</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C113" s="10">
         <v>20</v>
@@ -3547,7 +3717,7 @@
         <v>45457</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C114" s="10">
         <v>321</v>
@@ -3565,7 +3735,7 @@
         <v>45666</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C115" s="10">
         <v>329</v>
@@ -3583,7 +3753,7 @@
         <v>45908</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C116" s="10">
         <v>150</v>
@@ -3601,7 +3771,7 @@
         <v>45917</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C117" s="10">
         <v>50</v>
@@ -3619,7 +3789,7 @@
         <v>45959</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C118" s="10">
         <v>50</v>
@@ -3637,7 +3807,7 @@
         <v>45688</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C119" s="10">
         <v>10</v>
@@ -3655,7 +3825,7 @@
         <v>45689</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C120" s="10">
         <v>10</v>
@@ -3673,7 +3843,7 @@
         <v>45805</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C121" s="10">
         <v>30</v>
@@ -3691,7 +3861,7 @@
         <v>45923</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C122" s="10">
         <v>25</v>
@@ -3709,7 +3879,7 @@
         <v>46036</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C123" s="10">
         <v>15</v>
@@ -3727,7 +3897,7 @@
         <v>45924</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C124" s="10">
         <v>25</v>
@@ -3745,7 +3915,7 @@
         <v>45972</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C125" s="10">
         <v>10</v>
@@ -3763,7 +3933,7 @@
         <v>46052</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C126" s="2">
         <v>15</v>
@@ -3781,7 +3951,7 @@
         <v>45945</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C127" s="10">
         <v>1000</v>
@@ -3799,7 +3969,7 @@
         <v>45953</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C128" s="10">
         <v>100</v>
@@ -3817,7 +3987,7 @@
         <v>45958</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C129" s="10">
         <v>100</v>
@@ -3835,7 +4005,7 @@
         <v>45967</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C130" s="10">
         <v>100</v>
@@ -3853,7 +4023,7 @@
         <v>45968</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C131" s="10">
         <v>100</v>
@@ -3862,7 +4032,7 @@
         <v>99.98</v>
       </c>
       <c r="E131" s="9">
-        <f t="shared" ref="E131:E149" si="4">C131*D131</f>
+        <f t="shared" ref="E131:E156" si="4">C131*D131</f>
         <v>9998</v>
       </c>
     </row>
@@ -3871,7 +4041,7 @@
         <v>45971</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C132" s="10">
         <v>100</v>
@@ -3889,7 +4059,7 @@
         <v>45659</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C133" s="10">
         <v>100</v>
@@ -3907,7 +4077,7 @@
         <v>45660</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C134" s="10">
         <v>100</v>
@@ -3925,7 +4095,7 @@
         <v>45961</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C135" s="10">
         <v>200</v>
@@ -3943,7 +4113,7 @@
         <v>44789</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="C136" s="10">
         <v>5</v>
@@ -3961,7 +4131,7 @@
         <v>44789</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C137" s="10">
         <v>20</v>
@@ -3979,7 +4149,7 @@
         <v>45980</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="C138" s="2">
         <v>65</v>
@@ -3997,7 +4167,7 @@
         <v>45985</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="C139" s="2">
         <v>5</v>
@@ -4015,7 +4185,7 @@
         <v>46002</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="C140" s="2">
         <v>30</v>
@@ -4033,7 +4203,7 @@
         <v>45994</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="C141" s="2">
         <v>50</v>
@@ -4051,7 +4221,7 @@
         <v>46036</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="C142" s="2">
         <v>200</v>
@@ -4069,7 +4239,7 @@
         <v>46052</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="C143" s="2">
         <v>200</v>
@@ -4087,7 +4257,7 @@
         <v>46038</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="C144" s="2">
         <v>15</v>
@@ -4105,7 +4275,7 @@
         <v>46038</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="C145" s="2">
         <v>35</v>
@@ -4123,7 +4293,7 @@
         <v>46052</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="C146" s="2">
         <v>15</v>
@@ -4141,7 +4311,7 @@
         <v>46058</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="C147" s="2">
         <v>100</v>
@@ -4159,7 +4329,7 @@
         <v>46065</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="C148" s="2">
         <v>40</v>
@@ -4177,7 +4347,7 @@
         <v>46064</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="C149" s="2">
         <v>1400</v>
@@ -4188,6 +4358,132 @@
       <c r="E149" s="9">
         <f t="shared" si="4"/>
         <v>40614</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C150" s="2">
+        <v>10</v>
+      </c>
+      <c r="D150" s="12">
+        <v>47.62</v>
+      </c>
+      <c r="E150" s="9">
+        <f t="shared" si="4"/>
+        <v>476.2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="4">
+        <v>45355</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C151" s="2">
+        <v>7</v>
+      </c>
+      <c r="D151" s="12">
+        <v>43.47</v>
+      </c>
+      <c r="E151" s="9">
+        <f t="shared" si="4"/>
+        <v>304.28999999999996</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="4">
+        <v>45298</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C152" s="2">
+        <v>23</v>
+      </c>
+      <c r="D152" s="12">
+        <v>47.83</v>
+      </c>
+      <c r="E152" s="9">
+        <f t="shared" si="4"/>
+        <v>1100.0899999999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C153" s="2">
+        <v>10</v>
+      </c>
+      <c r="D153" s="12">
+        <v>51.15</v>
+      </c>
+      <c r="E153" s="9">
+        <f t="shared" si="4"/>
+        <v>511.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C154" s="2">
+        <v>10</v>
+      </c>
+      <c r="D154" s="12">
+        <v>48.2</v>
+      </c>
+      <c r="E154" s="9">
+        <f t="shared" si="4"/>
+        <v>482</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="4">
+        <v>45323</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C155" s="2">
+        <v>20</v>
+      </c>
+      <c r="D155" s="12">
+        <v>44.85</v>
+      </c>
+      <c r="E155" s="9">
+        <f t="shared" si="4"/>
+        <v>897</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C156" s="2">
+        <v>10</v>
+      </c>
+      <c r="D156" s="12">
+        <v>43.45</v>
+      </c>
+      <c r="E156" s="9">
+        <f t="shared" si="4"/>
+        <v>434.5</v>
       </c>
     </row>
   </sheetData>
@@ -4196,848 +4492,1785 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27997FB6-7343-4638-AF8E-E7E38DF71621}">
-  <dimension ref="A1:E49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A9703B6-8F70-4252-8AAF-09BC3D96BADE}">
+  <dimension ref="A1:T79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="15">
+        <v>2</v>
+      </c>
+      <c r="E2" s="15">
+        <v>16.5</v>
+      </c>
+      <c r="F2" s="15">
+        <v>33</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="15">
+        <v>5</v>
+      </c>
+      <c r="E3" s="15">
+        <v>18</v>
+      </c>
+      <c r="F3" s="15">
+        <v>90</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="15">
+        <v>40</v>
+      </c>
+      <c r="E4" s="15">
+        <v>17.5</v>
+      </c>
+      <c r="F4" s="15">
+        <v>700</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="15">
+        <v>12</v>
+      </c>
+      <c r="E5" s="15">
+        <v>1</v>
+      </c>
+      <c r="F5" s="15">
+        <v>12</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="19">
+        <v>3</v>
+      </c>
+      <c r="E6" s="19">
+        <v>225</v>
+      </c>
+      <c r="F6" s="19">
+        <v>675</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="19">
+        <v>2</v>
+      </c>
+      <c r="E7" s="19">
+        <v>17.5</v>
+      </c>
+      <c r="F7" s="19">
+        <v>35</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="19">
+        <v>5</v>
+      </c>
+      <c r="E8" s="19">
+        <v>31</v>
+      </c>
+      <c r="F8" s="19">
+        <v>155</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="19">
+        <v>100</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3.6</v>
+      </c>
+      <c r="F9" s="19">
+        <v>360</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="19">
+        <v>5</v>
+      </c>
+      <c r="E10" s="19">
+        <v>32</v>
+      </c>
+      <c r="F10" s="19">
+        <v>160</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="19">
+        <v>16</v>
+      </c>
+      <c r="E11" s="19">
+        <v>10</v>
+      </c>
+      <c r="F11" s="19">
+        <v>160</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="19">
+        <v>50</v>
+      </c>
+      <c r="E12" s="19">
+        <v>3</v>
+      </c>
+      <c r="F12" s="19">
+        <v>150</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="19">
+        <v>2</v>
+      </c>
+      <c r="E13" s="19">
+        <v>18</v>
+      </c>
+      <c r="F13" s="19">
+        <v>36</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="19">
+        <v>5</v>
+      </c>
+      <c r="E14" s="19">
+        <v>12</v>
+      </c>
+      <c r="F14" s="19">
+        <v>60</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="21">
+        <v>10</v>
+      </c>
+      <c r="E15" s="21">
+        <v>18</v>
+      </c>
+      <c r="F15" s="21">
+        <v>180</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="19">
+        <v>12</v>
+      </c>
+      <c r="E16" s="19">
+        <v>1</v>
+      </c>
+      <c r="F16" s="19">
+        <v>12</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="25">
+        <v>194</v>
+      </c>
+      <c r="E17" s="25">
+        <v>6.25</v>
+      </c>
+      <c r="F17" s="25">
+        <v>1212.5</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="19">
+        <v>20</v>
+      </c>
+      <c r="E18" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F18" s="19">
+        <v>50</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="19">
+        <v>25</v>
+      </c>
+      <c r="E19" s="19">
+        <v>19.5</v>
+      </c>
+      <c r="F19" s="19">
+        <v>487.5</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="19">
+        <v>2</v>
+      </c>
+      <c r="E20" s="19">
+        <v>20</v>
+      </c>
+      <c r="F20" s="19">
+        <v>40</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="19">
+        <v>2</v>
+      </c>
+      <c r="E21" s="19">
+        <v>8</v>
+      </c>
+      <c r="F21" s="19">
+        <v>16</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="25">
+        <v>200</v>
+      </c>
+      <c r="E22" s="25">
+        <v>7.5</v>
+      </c>
+      <c r="F22" s="25">
+        <v>1500</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="21">
+        <v>17</v>
+      </c>
+      <c r="E23" s="21">
+        <v>24</v>
+      </c>
+      <c r="F23" s="21">
+        <v>408</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="19">
+        <v>100</v>
+      </c>
+      <c r="E24" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="19">
+        <v>50</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="19">
+        <v>5</v>
+      </c>
+      <c r="E25" s="19">
+        <v>10</v>
+      </c>
+      <c r="F25" s="19">
+        <v>50</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="19">
+        <v>20</v>
+      </c>
+      <c r="E26" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="F26" s="19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="19">
+        <v>321</v>
+      </c>
+      <c r="E27" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="19">
+        <v>481.5</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C28" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D28" s="19">
+        <v>27</v>
+      </c>
+      <c r="E28" s="19">
+        <v>2</v>
+      </c>
+      <c r="F28" s="19">
+        <v>54</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C29" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="19">
+        <v>20</v>
+      </c>
+      <c r="E29" s="19">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F29" s="19">
+        <v>88</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="19">
+        <v>100</v>
+      </c>
+      <c r="E30" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="F30" s="19">
+        <v>150</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="19">
+        <v>88</v>
+      </c>
+      <c r="E31" s="19">
+        <v>1</v>
+      </c>
+      <c r="F31" s="19">
+        <v>88</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="19">
+        <v>75</v>
+      </c>
+      <c r="E32" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="F32" s="19">
+        <v>112.5</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D33" s="19">
+        <v>4</v>
+      </c>
+      <c r="E33" s="19">
+        <v>20</v>
+      </c>
+      <c r="F33" s="19">
+        <v>80</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="21">
+        <v>60</v>
+      </c>
+      <c r="E34" s="21">
+        <v>10</v>
+      </c>
+      <c r="F34" s="21">
+        <v>600</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="21">
+        <v>60</v>
+      </c>
+      <c r="E35" s="21">
+        <v>19</v>
+      </c>
+      <c r="F35" s="21">
+        <v>1140</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="19">
+        <v>10</v>
+      </c>
+      <c r="E36" s="19">
+        <v>4.25</v>
+      </c>
+      <c r="F36" s="19">
+        <v>42.5</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B2">
+      <c r="B37" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" s="31">
+        <v>200</v>
+      </c>
+      <c r="E37" s="31">
+        <v>6.5</v>
+      </c>
+      <c r="F37" s="31">
+        <v>1300</v>
+      </c>
+      <c r="G37" s="32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="19">
+        <v>80</v>
+      </c>
+      <c r="E38" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F38" s="19">
+        <v>200</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="19">
+        <v>100</v>
+      </c>
+      <c r="E39" s="19">
+        <v>15.9</v>
+      </c>
+      <c r="F39" s="19">
+        <v>1590</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" s="34">
+        <v>200</v>
+      </c>
+      <c r="E40" s="34">
+        <v>7.85</v>
+      </c>
+      <c r="F40" s="34">
+        <v>1570</v>
+      </c>
+      <c r="G40" s="35" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" s="19">
+        <v>30</v>
+      </c>
+      <c r="E41" s="19">
+        <v>8.25</v>
+      </c>
+      <c r="F41" s="19">
+        <v>247.5</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D42" s="19">
+        <v>600</v>
+      </c>
+      <c r="E42" s="19">
+        <v>3.6</v>
+      </c>
+      <c r="F42" s="19">
+        <v>2160</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="19">
+        <v>20</v>
+      </c>
+      <c r="E43" s="19">
+        <v>20.55</v>
+      </c>
+      <c r="F43" s="19">
+        <v>411</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="19">
+        <v>5</v>
+      </c>
+      <c r="E44" s="19">
+        <v>11</v>
+      </c>
+      <c r="F44" s="19">
+        <v>55</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="19">
+        <v>280</v>
+      </c>
+      <c r="E45" s="19">
+        <v>2.9</v>
+      </c>
+      <c r="F45" s="19">
+        <v>812</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="19">
+        <v>50</v>
+      </c>
+      <c r="E46" s="19">
+        <v>7</v>
+      </c>
+      <c r="F46" s="19">
+        <v>350</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="19">
+        <v>100</v>
+      </c>
+      <c r="E47" s="19">
+        <v>2.25</v>
+      </c>
+      <c r="F47" s="19">
+        <v>225</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" s="19">
+        <v>60</v>
+      </c>
+      <c r="E48" s="19">
+        <v>2.1</v>
+      </c>
+      <c r="F48" s="19">
+        <v>126</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49" s="21">
+        <v>80</v>
+      </c>
+      <c r="E49" s="21">
+        <v>24</v>
+      </c>
+      <c r="F49" s="21">
+        <v>1920</v>
+      </c>
+      <c r="G49" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" s="19">
+        <v>260</v>
+      </c>
+      <c r="E50" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="F50" s="19">
+        <v>130</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" s="19">
+        <v>158</v>
+      </c>
+      <c r="E51" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="F51" s="19">
+        <v>39.5</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D52" s="19">
+        <v>20</v>
+      </c>
+      <c r="E52" s="19">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F52" s="19">
+        <v>2.8</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D53" s="19">
+        <v>20</v>
+      </c>
+      <c r="E53" s="19">
+        <v>11</v>
+      </c>
+      <c r="F53" s="19">
+        <v>220</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D54" s="19">
+        <v>27</v>
+      </c>
+      <c r="E54" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F54" s="19">
+        <v>67.5</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D55" s="19">
+        <v>50</v>
+      </c>
+      <c r="E55" s="19">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F55" s="19">
+        <v>220</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D56" s="19">
+        <v>50</v>
+      </c>
+      <c r="E56" s="19">
+        <v>5</v>
+      </c>
+      <c r="F56" s="19">
+        <v>250</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" s="19">
+        <v>20</v>
+      </c>
+      <c r="E57" s="19">
+        <v>12.5</v>
+      </c>
+      <c r="F57" s="19">
+        <v>250</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D58" s="19">
+        <v>50</v>
+      </c>
+      <c r="E58" s="19">
+        <v>1.25</v>
+      </c>
+      <c r="F58" s="19">
+        <v>62.5</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="19">
+        <v>85</v>
+      </c>
+      <c r="E59" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="F59" s="19">
+        <v>127.5</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" s="19">
+        <v>4</v>
+      </c>
+      <c r="E60" s="19">
+        <v>18</v>
+      </c>
+      <c r="F60" s="19">
+        <v>72</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D61" s="19">
+        <v>20</v>
+      </c>
+      <c r="E61" s="19">
+        <v>11</v>
+      </c>
+      <c r="F61" s="19">
+        <v>220</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D62" s="19">
+        <v>40</v>
+      </c>
+      <c r="E62" s="19">
+        <v>23</v>
+      </c>
+      <c r="F62" s="19">
+        <v>920</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D63" s="21">
+        <v>90</v>
+      </c>
+      <c r="E63" s="21">
+        <v>19</v>
+      </c>
+      <c r="F63" s="21">
+        <v>1710</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D64" s="19">
+        <v>20</v>
+      </c>
+      <c r="E64" s="19">
+        <v>4.5</v>
+      </c>
+      <c r="F64" s="19">
+        <v>90</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D65" s="19">
+        <v>50</v>
+      </c>
+      <c r="E65" s="19">
+        <v>1.25</v>
+      </c>
+      <c r="F65" s="19">
+        <v>62.5</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O65" s="18"/>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="18"/>
+      <c r="R65" s="19"/>
+      <c r="S65" s="19"/>
+      <c r="T65" s="19"/>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D66" s="19">
+        <v>20</v>
+      </c>
+      <c r="E66" s="19">
+        <v>11</v>
+      </c>
+      <c r="F66" s="19">
+        <v>220</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O66" s="18"/>
+      <c r="P66" s="18"/>
+      <c r="Q66" s="18"/>
+      <c r="R66" s="19"/>
+      <c r="S66" s="19"/>
+      <c r="T66" s="19"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D67" s="19">
+        <v>20</v>
+      </c>
+      <c r="E67" s="19">
+        <v>46</v>
+      </c>
+      <c r="F67" s="19">
+        <v>920</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O67" s="18"/>
+      <c r="P67" s="18"/>
+      <c r="Q67" s="18"/>
+      <c r="R67" s="19"/>
+      <c r="S67" s="19"/>
+      <c r="T67" s="19"/>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D68" s="19">
+        <v>30</v>
+      </c>
+      <c r="E68" s="19">
+        <v>4</v>
+      </c>
+      <c r="F68" s="19">
+        <v>120</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O68" s="18"/>
+      <c r="P68" s="18"/>
+      <c r="Q68" s="18"/>
+      <c r="R68" s="19"/>
+      <c r="S68" s="19"/>
+      <c r="T68" s="19"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D69" s="19">
+        <v>40</v>
+      </c>
+      <c r="E69" s="19">
+        <v>6</v>
+      </c>
+      <c r="F69" s="19">
+        <v>240</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O69" s="18"/>
+      <c r="P69" s="18"/>
+      <c r="Q69" s="18"/>
+      <c r="R69" s="19"/>
+      <c r="S69" s="19"/>
+      <c r="T69" s="19"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="D70" s="19">
+        <v>50</v>
+      </c>
+      <c r="E70" s="19">
+        <v>1.3</v>
+      </c>
+      <c r="F70" s="19">
+        <v>65</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O70" s="18"/>
+      <c r="P70" s="18"/>
+      <c r="Q70" s="18"/>
+      <c r="R70" s="19"/>
+      <c r="S70" s="19"/>
+      <c r="T70" s="19"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D71" s="19">
         <v>300</v>
       </c>
-      <c r="C2">
-        <v>392.57</v>
-      </c>
-      <c r="D2">
-        <v>323.45</v>
-      </c>
-      <c r="E2">
-        <v>117769.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>20</v>
-      </c>
-      <c r="C3">
-        <v>593.72</v>
-      </c>
-      <c r="D3">
-        <v>182.1</v>
-      </c>
-      <c r="E3">
-        <v>11874.35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4">
-        <v>35</v>
-      </c>
-      <c r="C4">
-        <v>861.34</v>
-      </c>
-      <c r="D4">
-        <v>632</v>
-      </c>
-      <c r="E4">
-        <v>30146.75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <v>583.25</v>
-      </c>
-      <c r="D5">
-        <v>503.25</v>
-      </c>
-      <c r="E5">
-        <v>58325</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
+      <c r="E71" s="19">
+        <v>6.5</v>
+      </c>
+      <c r="F71" s="19">
+        <v>1950</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O71" s="18"/>
+      <c r="P71" s="18"/>
+      <c r="Q71" s="18"/>
+      <c r="R71" s="19"/>
+      <c r="S71" s="19"/>
+      <c r="T71" s="19"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D72" s="19">
         <v>50</v>
       </c>
-      <c r="C6">
-        <v>460.52</v>
-      </c>
-      <c r="D6">
-        <v>309</v>
-      </c>
-      <c r="E6">
-        <v>23026</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
-        <v>120</v>
-      </c>
-      <c r="C7">
-        <v>829.13</v>
-      </c>
-      <c r="D7">
-        <v>770.75</v>
-      </c>
-      <c r="E7">
-        <v>99495.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>1506.07</v>
-      </c>
-      <c r="D8">
-        <v>1285.1500000000001</v>
-      </c>
-      <c r="E8">
-        <v>45182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9">
-        <v>500</v>
-      </c>
-      <c r="C9">
-        <v>45.11</v>
-      </c>
-      <c r="D9">
-        <v>31.95</v>
-      </c>
-      <c r="E9">
-        <v>22552.78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>1500</v>
-      </c>
-      <c r="C10">
-        <v>59.59</v>
-      </c>
-      <c r="D10">
-        <v>55.44</v>
-      </c>
-      <c r="E10">
-        <v>89391.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>3452.85</v>
-      </c>
-      <c r="D11">
-        <v>3160.85</v>
-      </c>
-      <c r="E11">
-        <v>69057</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12">
-        <v>50</v>
-      </c>
-      <c r="C12">
-        <v>665.5</v>
-      </c>
-      <c r="D12">
-        <v>551</v>
-      </c>
-      <c r="E12">
-        <v>33275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>100</v>
-      </c>
-      <c r="C13">
-        <v>205.3</v>
-      </c>
-      <c r="D13">
-        <v>149.35</v>
-      </c>
-      <c r="E13">
-        <v>20530.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14">
-        <v>10</v>
-      </c>
-      <c r="C14">
-        <v>1396.05</v>
-      </c>
-      <c r="D14">
-        <v>927.1</v>
-      </c>
-      <c r="E14">
-        <v>13960.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15">
-        <v>70</v>
-      </c>
-      <c r="C15">
-        <v>876.03</v>
-      </c>
-      <c r="D15">
-        <v>812</v>
-      </c>
-      <c r="E15">
-        <v>61321.95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16">
-        <v>90</v>
-      </c>
-      <c r="C16">
-        <v>2446.4699999999998</v>
-      </c>
-      <c r="D16">
-        <v>2406</v>
-      </c>
-      <c r="E16">
-        <v>220182.45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17">
-        <v>2339.96</v>
-      </c>
-      <c r="D17">
-        <v>1688</v>
-      </c>
-      <c r="E17">
-        <v>9359.85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18">
-        <v>200</v>
-      </c>
-      <c r="C18">
-        <v>105.54</v>
-      </c>
-      <c r="D18">
-        <v>95.15</v>
-      </c>
-      <c r="E18">
-        <v>21108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19">
-        <v>200</v>
-      </c>
-      <c r="C19">
-        <v>138.77000000000001</v>
-      </c>
-      <c r="D19">
-        <v>128.43</v>
-      </c>
-      <c r="E19">
-        <v>27753.41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20">
-        <v>125</v>
-      </c>
-      <c r="C20">
-        <v>359.4</v>
-      </c>
-      <c r="D20">
-        <v>345.7</v>
-      </c>
-      <c r="E20">
-        <v>44925.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21">
-        <v>150</v>
-      </c>
-      <c r="C21">
-        <v>81.27</v>
-      </c>
-      <c r="D21">
-        <v>71.010000000000005</v>
-      </c>
-      <c r="E21">
-        <v>12190.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22">
-        <v>35</v>
-      </c>
-      <c r="C22">
-        <v>1037.8</v>
-      </c>
-      <c r="D22">
-        <v>994.15</v>
-      </c>
-      <c r="E22">
-        <v>36323</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23">
-        <v>15</v>
-      </c>
-      <c r="C23">
-        <v>2326.6999999999998</v>
-      </c>
-      <c r="D23">
-        <v>2264.1</v>
-      </c>
-      <c r="E23">
-        <v>34900.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24">
-        <v>30</v>
-      </c>
-      <c r="C24">
-        <v>1357.2</v>
-      </c>
-      <c r="D24">
-        <v>1326.6</v>
-      </c>
-      <c r="E24">
-        <v>40716</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25">
-        <v>20</v>
-      </c>
-      <c r="C25">
-        <v>2727.3</v>
-      </c>
-      <c r="D25">
-        <v>2704.4</v>
-      </c>
-      <c r="E25">
-        <v>54546</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26">
-        <v>100</v>
-      </c>
-      <c r="C26">
-        <v>477.06</v>
-      </c>
-      <c r="D26">
-        <v>473.7</v>
-      </c>
-      <c r="E26">
-        <v>47706.2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>115</v>
-      </c>
-      <c r="B27">
-        <v>5</v>
-      </c>
-      <c r="C27">
-        <v>1792.73</v>
-      </c>
-      <c r="D27">
-        <v>1796</v>
-      </c>
-      <c r="E27">
-        <v>8963.65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28">
-        <v>40</v>
-      </c>
-      <c r="C28">
-        <v>1332.4</v>
-      </c>
-      <c r="D28">
-        <v>1337.1</v>
-      </c>
-      <c r="E28">
-        <v>53296</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="E72" s="19">
+        <v>1.25</v>
+      </c>
+      <c r="F72" s="19">
+        <v>62.5</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="O72" s="18"/>
+      <c r="P72" s="18"/>
+      <c r="Q72" s="18"/>
+      <c r="R72" s="19"/>
+      <c r="S72" s="19"/>
+      <c r="T72" s="19"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B29">
+      <c r="B73" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D73" s="19">
         <v>400</v>
       </c>
-      <c r="C29">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="D29">
-        <v>76.400000000000006</v>
-      </c>
-      <c r="E29">
-        <v>30240</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30">
-        <v>200</v>
-      </c>
-      <c r="C30">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="D30">
-        <v>82.83</v>
-      </c>
-      <c r="E30">
-        <v>15379.32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31">
-        <v>18</v>
-      </c>
-      <c r="C31">
-        <v>1585.4</v>
-      </c>
-      <c r="D31">
-        <v>1672</v>
-      </c>
-      <c r="E31">
-        <v>28537.200000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32">
-        <v>20</v>
-      </c>
-      <c r="C32">
-        <v>31.57</v>
-      </c>
-      <c r="D32">
-        <v>151.4</v>
-      </c>
-      <c r="E32">
-        <v>631.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33">
-        <v>50</v>
-      </c>
-      <c r="C33">
-        <v>1265.25</v>
-      </c>
-      <c r="D33">
-        <v>1315.4</v>
-      </c>
-      <c r="E33">
-        <v>63262.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34">
-        <v>300</v>
-      </c>
-      <c r="C34">
-        <v>98.64</v>
-      </c>
-      <c r="D34">
-        <v>108.4</v>
-      </c>
-      <c r="E34">
-        <v>29592</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35">
-        <v>100</v>
-      </c>
-      <c r="C35">
-        <v>677.92</v>
-      </c>
-      <c r="D35">
-        <v>717</v>
-      </c>
-      <c r="E35">
-        <v>67792.36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36">
-        <v>200</v>
-      </c>
-      <c r="C36">
-        <v>401.05</v>
-      </c>
-      <c r="D36">
-        <v>422.11</v>
-      </c>
-      <c r="E36">
-        <v>80210.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37">
-        <v>100</v>
-      </c>
-      <c r="C37">
-        <v>665.47</v>
-      </c>
-      <c r="D37">
-        <v>711.8</v>
-      </c>
-      <c r="E37">
-        <v>66547.399999999994</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>2</v>
-      </c>
-      <c r="B38">
-        <v>200</v>
-      </c>
-      <c r="C38">
-        <v>339.58</v>
-      </c>
-      <c r="D38">
-        <v>367.25</v>
-      </c>
-      <c r="E38">
-        <v>67916.800000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39">
-        <v>300</v>
-      </c>
-      <c r="C39">
-        <v>246.14</v>
-      </c>
-      <c r="D39">
-        <v>269.3</v>
-      </c>
-      <c r="E39">
-        <v>73841.78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40">
-        <v>500</v>
-      </c>
-      <c r="C40">
-        <v>99.56</v>
-      </c>
-      <c r="D40">
-        <v>120.14</v>
-      </c>
-      <c r="E40">
-        <v>49782.1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41">
-        <v>150</v>
-      </c>
-      <c r="C41">
-        <v>352.72</v>
-      </c>
-      <c r="D41">
-        <v>424.2</v>
-      </c>
-      <c r="E41">
-        <v>52908.65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42">
-        <v>800</v>
-      </c>
-      <c r="C42">
-        <v>43.15</v>
-      </c>
-      <c r="D42">
-        <v>63.08</v>
-      </c>
-      <c r="E42">
-        <v>34523.1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43">
-        <v>100</v>
-      </c>
-      <c r="C43">
-        <v>799.61</v>
-      </c>
-      <c r="D43">
-        <v>1028.4000000000001</v>
-      </c>
-      <c r="E43">
-        <v>79961.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44">
+      <c r="E73" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F73" s="19">
         <v>1000</v>
       </c>
-      <c r="C44">
-        <v>108.97</v>
-      </c>
-      <c r="D44">
-        <v>132.54</v>
-      </c>
-      <c r="E44">
-        <v>108970</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45">
-        <v>530</v>
-      </c>
-      <c r="C45">
-        <v>177.31</v>
-      </c>
-      <c r="D45">
-        <v>302.5</v>
-      </c>
-      <c r="E45">
-        <v>93972.18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46">
-        <v>500</v>
-      </c>
-      <c r="C46">
-        <v>142.68</v>
-      </c>
-      <c r="D46">
-        <v>295.3</v>
-      </c>
-      <c r="E46">
-        <v>71338.759999999995</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>107</v>
-      </c>
-      <c r="B47">
-        <v>16</v>
-      </c>
-      <c r="C47">
-        <v>6213</v>
-      </c>
-      <c r="D47">
-        <v>19589</v>
-      </c>
-      <c r="E47">
-        <v>99408</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>25</v>
-      </c>
-      <c r="B48">
-        <v>7500</v>
-      </c>
-      <c r="C48">
-        <v>75.2</v>
-      </c>
-      <c r="D48">
-        <v>131.74</v>
-      </c>
-      <c r="E48">
-        <v>564019.43999999994</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49">
-        <v>500</v>
-      </c>
-      <c r="C49">
-        <v>99.79</v>
-      </c>
-      <c r="D49">
-        <v>127.49</v>
-      </c>
-      <c r="E49">
-        <v>49893</v>
-      </c>
+      <c r="G73" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="28"/>
+      <c r="B74" s="28"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="29"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L76" s="18"/>
+      <c r="M76" s="18"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="19"/>
+      <c r="P76" s="19"/>
+      <c r="Q76" s="19"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="19"/>
+      <c r="P77" s="19"/>
+      <c r="Q77" s="19"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L78" s="18"/>
+      <c r="M78" s="18"/>
+      <c r="N78" s="18"/>
+      <c r="O78" s="19"/>
+      <c r="P78" s="19"/>
+      <c r="Q78" s="19"/>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L79" s="18"/>
+      <c r="M79" s="18"/>
+      <c r="N79" s="18"/>
+      <c r="O79" s="19"/>
+      <c r="P79" s="19"/>
+      <c r="Q79" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5045,1245 +6278,619 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A82ABAA7-6A46-4F5E-969A-545287665DA9}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71786153-77BC-4AC6-BB59-60465E2F2330}">
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" t="s">
-        <v>123</v>
+      <c r="A1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>7500</v>
-      </c>
-      <c r="C2">
-        <v>75.2</v>
-      </c>
-      <c r="D2">
-        <v>132.71</v>
-      </c>
-      <c r="E2">
-        <v>564019.43999999994</v>
-      </c>
-      <c r="F2">
-        <v>995325</v>
+        <v>181</v>
+      </c>
+      <c r="B2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="15">
+        <v>500</v>
+      </c>
+      <c r="D2" s="15">
+        <v>12012</v>
+      </c>
+      <c r="E2" s="15">
+        <v>13940</v>
+      </c>
+      <c r="F2" s="15">
+        <v>1928</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>6213</v>
-      </c>
-      <c r="D3">
-        <v>17954.169999999998</v>
-      </c>
-      <c r="E3">
-        <v>99408</v>
-      </c>
-      <c r="F3">
-        <v>287266.71999999997</v>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="15">
+        <v>100</v>
+      </c>
+      <c r="D3" s="15">
+        <v>27980.95</v>
+      </c>
+      <c r="E3" s="15">
+        <v>41221</v>
+      </c>
+      <c r="F3" s="15">
+        <v>13240.05</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4">
-        <v>1000</v>
-      </c>
-      <c r="C4">
-        <v>108.97</v>
-      </c>
-      <c r="D4">
-        <v>133.52000000000001</v>
-      </c>
-      <c r="E4">
-        <v>108970</v>
-      </c>
-      <c r="F4">
-        <v>133520</v>
+        <v>183</v>
+      </c>
+      <c r="B4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="15">
+        <v>215</v>
+      </c>
+      <c r="D4" s="15">
+        <v>17914.900000000001</v>
+      </c>
+      <c r="E4" s="15">
+        <v>20723.849999999999</v>
+      </c>
+      <c r="F4" s="15">
+        <v>2808.95</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5">
-        <v>700</v>
-      </c>
-      <c r="C5">
-        <v>105.7</v>
-      </c>
-      <c r="D5">
-        <v>128.69999999999999</v>
-      </c>
-      <c r="E5">
-        <v>73993</v>
-      </c>
-      <c r="F5">
-        <v>90090</v>
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="15">
+        <v>100</v>
+      </c>
+      <c r="D5" s="15">
+        <v>14185</v>
+      </c>
+      <c r="E5" s="15">
+        <v>20320</v>
+      </c>
+      <c r="F5" s="15">
+        <v>6135</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>1100</v>
-      </c>
-      <c r="C6">
-        <v>236.44</v>
-      </c>
-      <c r="D6">
-        <v>247</v>
-      </c>
-      <c r="E6">
-        <v>260082.56</v>
-      </c>
-      <c r="F6">
-        <v>271700</v>
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="15">
+        <v>100</v>
+      </c>
+      <c r="D6" s="15">
+        <v>154344.15</v>
+      </c>
+      <c r="E6" s="15">
+        <v>174012.5</v>
+      </c>
+      <c r="F6" s="15">
+        <v>19668.349999999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7">
+        <v>185</v>
+      </c>
+      <c r="B7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="15">
+        <v>600</v>
+      </c>
+      <c r="D7" s="15">
+        <v>59910.7</v>
+      </c>
+      <c r="E7" s="15">
+        <v>111490</v>
+      </c>
+      <c r="F7" s="15">
+        <v>51579.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="15">
+        <v>72</v>
+      </c>
+      <c r="D8" s="15">
+        <v>32271.45</v>
+      </c>
+      <c r="E8" s="15">
+        <v>39967.199999999997</v>
+      </c>
+      <c r="F8" s="15">
+        <v>7695.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="15">
+        <v>4</v>
+      </c>
+      <c r="D9" s="15">
+        <v>9828</v>
+      </c>
+      <c r="E9" s="15">
+        <v>10620.2</v>
+      </c>
+      <c r="F9" s="15">
+        <v>792.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="15">
+        <v>24</v>
+      </c>
+      <c r="D10" s="15">
+        <v>37805.599999999999</v>
+      </c>
+      <c r="E10" s="15">
+        <v>43501.1</v>
+      </c>
+      <c r="F10" s="15">
+        <v>5695.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="15">
+        <v>25</v>
+      </c>
+      <c r="D11" s="15">
+        <v>12351.25</v>
+      </c>
+      <c r="E11" s="15">
+        <v>14517.5</v>
+      </c>
+      <c r="F11" s="15">
+        <v>2166.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="15">
+        <v>256</v>
+      </c>
+      <c r="D12" s="15">
+        <v>39343.699999999997</v>
+      </c>
+      <c r="E12" s="15">
+        <v>42022.3</v>
+      </c>
+      <c r="F12" s="15">
+        <v>2678.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="15">
+        <v>3</v>
+      </c>
+      <c r="D13" s="15">
+        <v>9630.7000000000007</v>
+      </c>
+      <c r="E13" s="15">
+        <v>11460.15</v>
+      </c>
+      <c r="F13" s="15">
+        <v>1829.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" s="15">
+        <v>25</v>
+      </c>
+      <c r="D14" s="15">
+        <v>30718.75</v>
+      </c>
+      <c r="E14" s="15">
+        <v>35967.5</v>
+      </c>
+      <c r="F14" s="15">
+        <v>5248.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="15">
+        <v>200</v>
+      </c>
+      <c r="D15" s="15">
+        <v>26636</v>
+      </c>
+      <c r="E15" s="15">
+        <v>30276</v>
+      </c>
+      <c r="F15" s="15">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="15">
+        <v>40</v>
+      </c>
+      <c r="D16" s="15">
+        <v>29198.75</v>
+      </c>
+      <c r="E16" s="15">
+        <v>40360.800000000003</v>
+      </c>
+      <c r="F16" s="15">
+        <v>11162.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" s="15">
+        <v>26</v>
+      </c>
+      <c r="D17" s="15">
+        <v>9710.74</v>
+      </c>
+      <c r="E17" s="15">
+        <v>11346.4</v>
+      </c>
+      <c r="F17" s="15">
+        <v>1635.66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="15">
+        <v>10</v>
+      </c>
+      <c r="D18" s="15">
+        <v>7292.59</v>
+      </c>
+      <c r="E18" s="15">
+        <v>8272</v>
+      </c>
+      <c r="F18" s="15">
+        <v>979.41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" s="15">
+        <v>530</v>
+      </c>
+      <c r="D19" s="15">
+        <v>93972.18</v>
+      </c>
+      <c r="E19" s="15">
+        <v>176156.4</v>
+      </c>
+      <c r="F19" s="15">
+        <v>82184.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" s="15">
+        <v>51</v>
+      </c>
+      <c r="D20" s="15">
+        <v>13014.6</v>
+      </c>
+      <c r="E20" s="15">
+        <v>14559.99</v>
+      </c>
+      <c r="F20" s="15">
+        <v>1545.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B21" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="15">
+        <v>2871</v>
+      </c>
+      <c r="D21" s="15">
+        <v>173526.92</v>
+      </c>
+      <c r="E21" s="15">
+        <v>225800.9</v>
+      </c>
+      <c r="F21" s="15">
+        <v>52273.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="15">
+        <v>449</v>
+      </c>
+      <c r="D22" s="15">
+        <v>109351.54</v>
+      </c>
+      <c r="E22" s="15">
+        <v>121695.49</v>
+      </c>
+      <c r="F22" s="15">
+        <v>12343.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="15">
+        <v>46</v>
+      </c>
+      <c r="D23" s="15">
+        <v>21708.77</v>
+      </c>
+      <c r="E23" s="15">
+        <v>24326.05</v>
+      </c>
+      <c r="F23" s="15">
+        <v>2617.2800000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C24" s="15">
+        <v>32</v>
+      </c>
+      <c r="D24" s="15">
+        <v>25378.55</v>
+      </c>
+      <c r="E24" s="15">
+        <v>33151.15</v>
+      </c>
+      <c r="F24" s="15">
+        <v>7772.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="15">
+        <v>30</v>
+      </c>
+      <c r="D25" s="15">
+        <v>28597.5</v>
+      </c>
+      <c r="E25" s="15">
+        <v>32895</v>
+      </c>
+      <c r="F25" s="15">
+        <v>4297.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="15">
+        <v>800</v>
+      </c>
+      <c r="D26" s="15">
+        <v>113807.5</v>
+      </c>
+      <c r="E26" s="15">
+        <v>135700.20000000001</v>
+      </c>
+      <c r="F26" s="15">
+        <v>21892.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="15">
+        <v>5</v>
+      </c>
+      <c r="D27" s="15">
+        <v>5787.75</v>
+      </c>
+      <c r="E27" s="15">
+        <v>6664.75</v>
+      </c>
+      <c r="F27" s="15">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="15">
         <v>100</v>
       </c>
-      <c r="C7">
-        <v>23.48</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>2348</v>
-      </c>
-      <c r="F7">
-        <v>2500</v>
+      <c r="D28" s="15">
+        <v>54976.25</v>
+      </c>
+      <c r="E28" s="15">
+        <v>67055</v>
+      </c>
+      <c r="F28" s="15">
+        <v>14355.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="15">
+        <v>160</v>
+      </c>
+      <c r="D29" s="15">
+        <v>44777</v>
+      </c>
+      <c r="E29" s="15">
+        <v>49826</v>
+      </c>
+      <c r="F29" s="15">
+        <v>5049</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="15">
+        <v>12</v>
+      </c>
+      <c r="D30" s="15">
+        <v>5257.8</v>
+      </c>
+      <c r="E30" s="15">
+        <v>5967</v>
+      </c>
+      <c r="F30" s="15">
+        <v>709.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EDC0E13-5D19-484C-8122-D5DFA7299F88}">
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="2">
-        <v>18952</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>24929.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="2">
-        <v>20734.099999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="2">
-        <v>39459.31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="2">
-        <v>41072.22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="2">
-        <v>111854.62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="63" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="2">
-        <v>87828.459999999992</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2">
-        <v>21196.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="2">
-        <v>87519.77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="2">
-        <v>118560</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="2">
-        <v>155426.76999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="2">
-        <v>57976.32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="2">
-        <v>127761</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="2">
-        <v>175257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="2">
-        <v>36017.800000000003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="2">
-        <v>167856.92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="2">
-        <v>56037.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="63" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="2">
-        <v>98232.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="2">
-        <v>59034.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="2">
-        <v>110342</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="2">
-        <v>303581</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="2">
-        <v>100934</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="63" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="2">
-        <v>44196</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="267.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="2">
-        <v>324521.95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="2">
-        <v>360648.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="63" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="2">
-        <v>93133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="63" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="2">
-        <v>56294</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="9"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50651BF0-43B4-4F5A-8863-9FB8145C4A50}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="2">
-        <v>18952</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="2">
-        <v>85122.91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="330" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4">
-        <v>1020471</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5">
-        <v>1718517</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8832F1D9-872C-4FF9-80E8-CB7048844081}">
-  <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>20</v>
-      </c>
-      <c r="C2">
-        <v>2727.3</v>
-      </c>
-      <c r="D2">
-        <v>54546</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>100</v>
-      </c>
-      <c r="C3">
-        <v>665.47</v>
-      </c>
-      <c r="D3">
-        <v>66547.399999999994</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>18</v>
-      </c>
-      <c r="C4">
-        <v>1585.4</v>
-      </c>
-      <c r="D4">
-        <v>28537.200000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>90</v>
-      </c>
-      <c r="C5">
-        <v>2446.4699999999998</v>
-      </c>
-      <c r="D5">
-        <v>220182.45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <v>200</v>
-      </c>
-      <c r="C6">
-        <v>143.37</v>
-      </c>
-      <c r="D6">
-        <v>28674</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>799.61</v>
-      </c>
-      <c r="D7">
-        <v>79961.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>300</v>
-      </c>
-      <c r="C8">
-        <v>392.57</v>
-      </c>
-      <c r="D8">
-        <v>117769.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9">
-        <v>30</v>
-      </c>
-      <c r="C9">
-        <v>1763.62</v>
-      </c>
-      <c r="D9">
-        <v>52908.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>3452.85</v>
-      </c>
-      <c r="D10">
-        <v>69057</v>
-      </c>
-      <c r="E10">
-        <f>SUM(D2:D10)</f>
-        <v>718183.65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12">
-        <v>100</v>
-      </c>
-      <c r="C12">
-        <v>357.2</v>
-      </c>
-      <c r="D12">
-        <v>35720</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13">
-        <v>500</v>
-      </c>
-      <c r="C13">
-        <v>99.56</v>
-      </c>
-      <c r="D13">
-        <v>49782.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14">
-        <v>300</v>
-      </c>
-      <c r="C14">
-        <v>98.64</v>
-      </c>
-      <c r="D14">
-        <v>29592</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>1543.3</v>
-      </c>
-      <c r="D15">
-        <v>30866</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16">
-        <v>25</v>
-      </c>
-      <c r="C16">
-        <v>1327.3</v>
-      </c>
-      <c r="D16">
-        <v>33182.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17">
-        <v>100</v>
-      </c>
-      <c r="C17">
-        <v>477.06</v>
-      </c>
-      <c r="D17">
-        <v>47706.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-      <c r="C18">
-        <v>665.5</v>
-      </c>
-      <c r="D18">
-        <v>33275</v>
-      </c>
-      <c r="E18">
-        <f>SUM(D12:D18)</f>
-        <v>260123.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20">
-        <v>400</v>
-      </c>
-      <c r="C20">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="D20">
-        <v>30240</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21">
-        <v>500</v>
-      </c>
-      <c r="C21">
-        <v>45.11</v>
-      </c>
-      <c r="D21">
-        <v>22552.78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22">
-        <v>5</v>
-      </c>
-      <c r="C22">
-        <v>1792.73</v>
-      </c>
-      <c r="D22">
-        <v>8963.65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23">
-        <v>100</v>
-      </c>
-      <c r="C23">
-        <v>583.25</v>
-      </c>
-      <c r="D23">
-        <v>58325</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24">
-        <v>70</v>
-      </c>
-      <c r="C24">
-        <v>876.03</v>
-      </c>
-      <c r="D24">
-        <v>61321.95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25">
-        <v>100</v>
-      </c>
-      <c r="C25">
-        <v>205.3</v>
-      </c>
-      <c r="D25">
-        <v>20530.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26">
-        <v>20</v>
-      </c>
-      <c r="C26">
-        <v>31.57</v>
-      </c>
-      <c r="D26">
-        <v>631.35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27">
-        <v>120</v>
-      </c>
-      <c r="C27">
-        <v>829.13</v>
-      </c>
-      <c r="D27">
-        <v>99495.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28">
-        <v>20</v>
-      </c>
-      <c r="C28">
-        <v>593.72</v>
-      </c>
-      <c r="D28">
-        <v>11874.35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29">
-        <v>35</v>
-      </c>
-      <c r="C29">
-        <v>861.34</v>
-      </c>
-      <c r="D29">
-        <v>30146.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30">
-        <v>10</v>
-      </c>
-      <c r="C30">
-        <v>1396.05</v>
-      </c>
-      <c r="D30">
-        <v>13960.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31">
-        <v>200</v>
-      </c>
-      <c r="C31">
-        <v>339.58</v>
-      </c>
-      <c r="D31">
-        <v>67916.800000000003</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32">
-        <v>150</v>
-      </c>
-      <c r="C32">
-        <v>81.27</v>
-      </c>
-      <c r="D32">
-        <v>12190.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <v>800</v>
-      </c>
-      <c r="C33">
-        <v>43.15</v>
-      </c>
-      <c r="D33">
-        <v>34523.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34">
-        <v>200</v>
-      </c>
-      <c r="C34">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="D34">
-        <v>15379.32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35">
-        <v>30</v>
-      </c>
-      <c r="C35">
-        <v>1357.2</v>
-      </c>
-      <c r="D35">
-        <v>40716</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36">
-        <v>4</v>
-      </c>
-      <c r="C36">
-        <v>2339.96</v>
-      </c>
-      <c r="D36">
-        <v>9359.85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37">
-        <v>50</v>
-      </c>
-      <c r="C37">
-        <v>1265.25</v>
-      </c>
-      <c r="D37">
-        <v>63262.7</v>
-      </c>
-      <c r="E37">
-        <f>SUM(D20:D37)</f>
-        <v>601389.99999999988</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39">
-        <v>400</v>
-      </c>
-      <c r="C39">
-        <v>247.35</v>
-      </c>
-      <c r="D39">
-        <v>98940.78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40">
-        <v>100</v>
-      </c>
-      <c r="C40">
-        <v>677.92</v>
-      </c>
-      <c r="D40">
-        <v>67792.36</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41">
-        <v>200</v>
-      </c>
-      <c r="C41">
-        <v>138.77000000000001</v>
-      </c>
-      <c r="D41">
-        <v>27753.41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>5</v>
-      </c>
-      <c r="B42">
-        <v>1500</v>
-      </c>
-      <c r="C42">
-        <v>59.59</v>
-      </c>
-      <c r="D42">
-        <v>89391.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>23</v>
-      </c>
-      <c r="B43">
-        <v>200</v>
-      </c>
-      <c r="C43">
-        <v>401.05</v>
-      </c>
-      <c r="D43">
-        <v>80210.5</v>
-      </c>
-      <c r="E43">
-        <f>SUM(D39:D43)</f>
-        <v>364088.35000000003</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45">
-        <v>16</v>
-      </c>
-      <c r="C45">
-        <v>6213</v>
-      </c>
-      <c r="D45">
-        <v>99408</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46">
-        <v>500</v>
-      </c>
-      <c r="C46">
-        <v>99.79</v>
-      </c>
-      <c r="D46">
-        <v>49893</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>25</v>
-      </c>
-      <c r="B47">
-        <v>6800</v>
-      </c>
-      <c r="C47">
-        <v>69.64</v>
-      </c>
-      <c r="D47">
-        <v>473537.43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48">
-        <v>500</v>
-      </c>
-      <c r="C48">
-        <v>170.25</v>
-      </c>
-      <c r="D48">
-        <v>85127.28</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49">
-        <v>1000</v>
-      </c>
-      <c r="C49">
-        <v>108.97</v>
-      </c>
-      <c r="D49">
-        <v>108970</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50">
-        <v>700</v>
-      </c>
-      <c r="C50">
-        <v>134.12</v>
-      </c>
-      <c r="D50">
-        <v>93882.76</v>
-      </c>
-      <c r="E50">
-        <f>SUM(D45:D50)</f>
-        <v>910818.47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Holdings14feb2026.xlsx
+++ b/Holdings14feb2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Investment\pms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE73C0E1-49C5-4671-BB8B-54EE7B20F198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8223B528-08A7-49B9-A9D2-142EB5DBD7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="217">
   <si>
     <t>ASIANPAINT</t>
   </si>
@@ -681,6 +681,9 @@
   </si>
   <si>
     <t>26/06/2025</t>
+  </si>
+  <si>
+    <t>27/2/2026</t>
   </si>
 </sst>
 </file>
@@ -1666,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A34EE69-FFA9-4CB2-92C6-25BBB6E0EE9A}">
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -4032,7 +4035,7 @@
         <v>99.98</v>
       </c>
       <c r="E131" s="9">
-        <f t="shared" ref="E131:E156" si="4">C131*D131</f>
+        <f t="shared" ref="E131:E157" si="4">C131*D131</f>
         <v>9998</v>
       </c>
     </row>
@@ -4091,39 +4094,39 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="4">
-        <v>45961</v>
+      <c r="A135" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C135" s="10">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D135" s="13">
-        <v>138.77000000000001</v>
+        <v>131.43</v>
       </c>
       <c r="E135" s="9">
         <f t="shared" si="4"/>
-        <v>27754.000000000004</v>
+        <v>13143</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
-        <v>44789</v>
+        <v>45961</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>209</v>
+        <v>44</v>
       </c>
       <c r="C136" s="10">
-        <v>5</v>
-      </c>
-      <c r="D136" s="12">
-        <v>1792</v>
+        <v>200</v>
+      </c>
+      <c r="D136" s="13">
+        <v>138.77000000000001</v>
       </c>
       <c r="E136" s="9">
         <f t="shared" si="4"/>
-        <v>8960</v>
+        <v>27754.000000000004</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -4131,112 +4134,112 @@
         <v>44789</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="C137" s="10">
-        <v>20</v>
-      </c>
-      <c r="D137" s="13">
-        <v>31.57</v>
+        <v>5</v>
+      </c>
+      <c r="D137" s="12">
+        <v>1792</v>
       </c>
       <c r="E137" s="9">
         <f t="shared" si="4"/>
-        <v>631.4</v>
+        <v>8960</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
-        <v>45980</v>
+        <v>44789</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C138" s="2">
-        <v>65</v>
-      </c>
-      <c r="D138" s="12">
-        <v>616</v>
+        <v>45</v>
+      </c>
+      <c r="C138" s="10">
+        <v>20</v>
+      </c>
+      <c r="D138" s="13">
+        <v>31.57</v>
       </c>
       <c r="E138" s="9">
         <f t="shared" si="4"/>
-        <v>40040</v>
+        <v>631.4</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>45985</v>
+        <v>45980</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C139" s="2">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D139" s="12">
-        <v>571.25</v>
+        <v>616</v>
       </c>
       <c r="E139" s="9">
         <f t="shared" si="4"/>
-        <v>2856.25</v>
+        <v>40040</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
-        <v>46002</v>
+        <v>45985</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C140" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D140" s="12">
-        <v>514.25</v>
+        <v>571.25</v>
       </c>
       <c r="E140" s="9">
         <f t="shared" si="4"/>
-        <v>15427.5</v>
+        <v>2856.25</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C141" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D141" s="12">
-        <v>665.5</v>
+        <v>514.25</v>
       </c>
       <c r="E141" s="9">
         <f t="shared" si="4"/>
-        <v>33275</v>
+        <v>15427.5</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
-        <v>46036</v>
+        <v>45994</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C142" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D142" s="12">
-        <v>105.18</v>
+        <v>665.5</v>
       </c>
       <c r="E142" s="9">
         <f t="shared" si="4"/>
-        <v>21036</v>
+        <v>33275</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>46052</v>
+        <v>46036</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>49</v>
@@ -4244,30 +4247,30 @@
       <c r="C143" s="2">
         <v>200</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="12">
+        <v>105.18</v>
+      </c>
+      <c r="E143" s="9">
+        <f t="shared" si="4"/>
+        <v>21036</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="4">
+        <v>46052</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C144" s="2">
+        <v>200</v>
+      </c>
+      <c r="D144" s="2">
         <v>99.39</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E144" s="2">
         <f t="shared" si="4"/>
         <v>19878</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="4">
-        <v>46038</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C144" s="2">
-        <v>15</v>
-      </c>
-      <c r="D144" s="12">
-        <v>2326.6999999999998</v>
-      </c>
-      <c r="E144" s="9">
-        <f t="shared" si="4"/>
-        <v>34900.5</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -4275,213 +4278,231 @@
         <v>46038</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C145" s="2">
-        <v>35</v>
-      </c>
-      <c r="D145" s="2">
-        <v>1037.8</v>
+        <v>15</v>
+      </c>
+      <c r="D145" s="12">
+        <v>2326.6999999999998</v>
       </c>
       <c r="E145" s="9">
         <f t="shared" si="4"/>
-        <v>36323</v>
+        <v>34900.5</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
-        <v>46052</v>
+        <v>46038</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C146" s="2">
-        <v>15</v>
-      </c>
-      <c r="D146" s="9">
-        <v>951.3</v>
+        <v>35</v>
+      </c>
+      <c r="D146" s="2">
+        <v>1037.8</v>
       </c>
       <c r="E146" s="9">
         <f t="shared" si="4"/>
-        <v>14269.5</v>
+        <v>36323</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C147" s="2">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D147" s="9">
-        <v>23.48</v>
+        <v>951.3</v>
       </c>
       <c r="E147" s="9">
-        <f>C147*D147</f>
-        <v>2348</v>
+        <f t="shared" si="4"/>
+        <v>14269.5</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
-        <v>46065</v>
+        <v>46058</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C148" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D148" s="9">
-        <v>25</v>
+        <v>23.48</v>
       </c>
       <c r="E148" s="9">
         <f>C148*D148</f>
-        <v>1000</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
+        <v>46065</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C149" s="2">
+        <v>40</v>
+      </c>
+      <c r="D149" s="9">
+        <v>25</v>
+      </c>
+      <c r="E149" s="9">
+        <f>C149*D149</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="4">
         <v>46064</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B150" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C150" s="2">
         <v>1400</v>
       </c>
-      <c r="D149" s="9">
+      <c r="D150" s="9">
         <v>29.01</v>
       </c>
-      <c r="E149" s="9">
+      <c r="E150" s="9">
         <f t="shared" si="4"/>
         <v>40614</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="2" t="s">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B151" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C151" s="2">
         <v>10</v>
       </c>
-      <c r="D150" s="12">
+      <c r="D151" s="12">
         <v>47.62</v>
       </c>
-      <c r="E150" s="9">
+      <c r="E151" s="9">
         <f t="shared" si="4"/>
         <v>476.2</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="4">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="4">
         <v>45355</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B152" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C152" s="2">
         <v>7</v>
       </c>
-      <c r="D151" s="12">
+      <c r="D152" s="12">
         <v>43.47</v>
       </c>
-      <c r="E151" s="9">
+      <c r="E152" s="9">
         <f t="shared" si="4"/>
         <v>304.28999999999996</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="4">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="4">
         <v>45298</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B153" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C153" s="2">
         <v>23</v>
       </c>
-      <c r="D152" s="12">
+      <c r="D153" s="12">
         <v>47.83</v>
       </c>
-      <c r="E152" s="9">
+      <c r="E153" s="9">
         <f t="shared" si="4"/>
         <v>1100.0899999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="2" t="s">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="B154" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C154" s="2">
         <v>10</v>
       </c>
-      <c r="D153" s="12">
+      <c r="D154" s="12">
         <v>51.15</v>
       </c>
-      <c r="E153" s="9">
+      <c r="E154" s="9">
         <f t="shared" si="4"/>
         <v>511.5</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="2" t="s">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B155" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C155" s="2">
         <v>10</v>
       </c>
-      <c r="D154" s="12">
+      <c r="D155" s="12">
         <v>48.2</v>
       </c>
-      <c r="E154" s="9">
+      <c r="E155" s="9">
         <f t="shared" si="4"/>
         <v>482</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="4">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="4">
         <v>45323</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B156" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C156" s="2">
         <v>20</v>
       </c>
-      <c r="D155" s="12">
+      <c r="D156" s="12">
         <v>44.85</v>
       </c>
-      <c r="E155" s="9">
+      <c r="E156" s="9">
         <f t="shared" si="4"/>
         <v>897</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B157" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C157" s="2">
         <v>10</v>
       </c>
-      <c r="D156" s="12">
+      <c r="D157" s="12">
         <v>43.45</v>
       </c>
-      <c r="E156" s="9">
+      <c r="E157" s="9">
         <f t="shared" si="4"/>
         <v>434.5</v>
       </c>
